--- a/output/pdf_financials_xlsx/TRI.xlsx
+++ b/output/pdf_financials_xlsx/TRI.xlsx
@@ -2410,37 +2410,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>818</v>
+        <v>657</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>859</v>
+        <v>683</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>874</v>
+        <v>686</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>646</v>
+        <v>548</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>502</v>
+        <v>426</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1079</v>
+        <v>546</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>618</v>
+        <v>510</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>673</v>
+        <v>469</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>501</v>
+        <v>435</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>435</v>
+        <v>400</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>574</v>
+        <v>480</v>
       </c>
     </row>
     <row r="49">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -12646,7 +12646,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -14721,7 +14721,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>CurrentAssets</t>
+          <t>OtherCurrentAssets</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">

--- a/output/pdf_financials_xlsx/TRI.xlsx
+++ b/output/pdf_financials_xlsx/TRI.xlsx
@@ -2410,37 +2410,37 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>657</v>
+        <v>818</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>683</v>
+        <v>859</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>686</v>
+        <v>874</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>548</v>
+        <v>646</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>426</v>
+        <v>502</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>546</v>
+        <v>1079</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>510</v>
+        <v>618</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>469</v>
+        <v>673</v>
       </c>
       <c r="J48" s="3" t="n">
+        <v>501</v>
+      </c>
+      <c r="K48" s="3" t="n">
         <v>435</v>
       </c>
-      <c r="K48" s="3" t="n">
-        <v>400</v>
-      </c>
       <c r="L48" s="3" t="n">
-        <v>480</v>
+        <v>574</v>
       </c>
     </row>
     <row r="49">
@@ -3934,37 +3934,37 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>2171</v>
+        <v>11341</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>2124</v>
+        <v>10605</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>2258</v>
+        <v>10034</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>1740</v>
+        <v>8109</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>1124</v>
+        <v>5117</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>1264</v>
+        <v>4516</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>709</v>
+        <v>5734</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>691</v>
+        <v>4935</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>692</v>
+        <v>4387</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>675</v>
+        <v>2995</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>656</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="86">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>OtherNonCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>OtherNonCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -12646,7 +12646,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -13416,7 +13416,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>OtherNonCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -14721,7 +14721,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
@@ -15448,7 +15448,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>OtherNonCurrentLiabilities</t>
+          <t>CurrentLiabilities</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">

--- a/output/pdf_financials_xlsx/TRI.xlsx
+++ b/output/pdf_financials_xlsx/TRI.xlsx
@@ -4993,10 +4993,10 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -5541,16 +5541,16 @@
         </is>
       </c>
       <c r="B126" s="3" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="C126" s="3" t="n">
-        <v>0</v>
+        <v>-53</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0</v>
+        <v>-57</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0</v>
+        <v>-66</v>
       </c>
       <c r="F126" s="3" t="n">
         <v>0</v>
@@ -20155,7 +20155,11 @@
           <t>Proceeds from disposals of property and equipment</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -21832,7 +21836,11 @@
           <t>Dividends paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E247" s="5" t="n">
         <v>-48</v>
       </c>

--- a/output/pdf_financials_xlsx/TRI.xlsx
+++ b/output/pdf_financials_xlsx/TRI.xlsx
@@ -5341,37 +5341,37 @@
         </is>
       </c>
       <c r="B121" s="3" t="n">
-        <v>0</v>
+        <v>-1023</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-1417</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-1673</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>0</v>
+        <v>-1174</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-488</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-1282</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-1079</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-639</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="122">
@@ -16944,7 +16944,11 @@
           <t>Repurchases of common shares 25</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -19599,7 +19603,11 @@
           <t>Repurchases of common shares 24</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -21702,7 +21710,11 @@
           <t>Repurchases of common shares 23</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -22546,7 +22558,11 @@
           <t>Repurchases of common shares 22</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E257" s="5" t="n">
         <v>-1023</v>
       </c>
